--- a/data/trans_orig/IP2901-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2901-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>12853</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26227</t>
+          <t>26049</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19526</t>
+          <t>20104</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34423</t>
+          <t>35432</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35415</t>
+          <t>35932</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55678</t>
+          <t>54418</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14634</t>
+          <t>14206</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16257</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13583</t>
+          <t>13495</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27474</t>
+          <t>26888</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>102186</t>
+          <t>101914</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117516</t>
+          <t>117526</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>105749</t>
+          <t>104844</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>122350</t>
+          <t>121997</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>212620</t>
+          <t>212915</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>235987</t>
+          <t>235604</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,52%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28703</t>
+          <t>28923</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45330</t>
+          <t>45955</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39243</t>
+          <t>38175</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58303</t>
+          <t>58642</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>72936</t>
+          <t>72062</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>96940</t>
+          <t>97157</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>8462</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19331</t>
+          <t>19253</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20485</t>
+          <t>20989</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19954</t>
+          <t>20195</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>35449</t>
+          <t>35953</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>133740</t>
+          <t>132015</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>151603</t>
+          <t>150423</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>136292</t>
+          <t>136477</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157944</t>
+          <t>157852</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>277857</t>
+          <t>276855</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>304366</t>
+          <t>304773</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,81%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20116</t>
+          <t>19919</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33775</t>
+          <t>33897</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16352</t>
+          <t>16394</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29845</t>
+          <t>30680</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39987</t>
+          <t>40012</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60116</t>
+          <t>59625</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14846</t>
+          <t>14270</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20877</t>
+          <t>21251</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>17296</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32024</t>
+          <t>32200</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92295</t>
+          <t>93523</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>108205</t>
+          <t>109446</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>100739</t>
+          <t>100380</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>117159</t>
+          <t>118022</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>198618</t>
+          <t>198605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>221454</t>
+          <t>221098</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,81%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30876</t>
+          <t>30696</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48967</t>
+          <t>50337</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28979</t>
+          <t>28565</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46962</t>
+          <t>46316</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64221</t>
+          <t>62869</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90034</t>
+          <t>90699</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12836</t>
+          <t>12438</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14818</t>
+          <t>15203</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23823</t>
+          <t>23146</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>146064</t>
+          <t>144566</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>165603</t>
+          <t>165865</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>144319</t>
+          <t>143361</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>164406</t>
+          <t>162775</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>295732</t>
+          <t>295172</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>323858</t>
+          <t>325233</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>104389</t>
+          <t>105748</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>135366</t>
+          <t>135276</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>119187</t>
+          <t>117588</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>153500</t>
+          <t>150193</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>230396</t>
+          <t>232945</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>275478</t>
+          <t>278081</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30367</t>
+          <t>29718</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49751</t>
+          <t>49112</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38277</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>60339</t>
+          <t>60056</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>73828</t>
+          <t>73967</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>101346</t>
+          <t>103102</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>492897</t>
+          <t>494202</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>528087</t>
+          <t>527609</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>506028</t>
+          <t>506989</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>542538</t>
+          <t>544127</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1013630</t>
+          <t>1010789</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1061918</t>
+          <t>1061822</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,05%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18529</t>
+          <t>18760</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34284</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24889</t>
+          <t>24297</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41564</t>
+          <t>41208</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47248</t>
+          <t>46616</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69308</t>
+          <t>69740</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2279</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10977</t>
+          <t>10424</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17517</t>
+          <t>17654</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10175</t>
+          <t>10512</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23622</t>
+          <t>23306</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100312</t>
+          <t>98892</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>116002</t>
+          <t>115803</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>97270</t>
+          <t>98052</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>116465</t>
+          <t>116164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>202686</t>
+          <t>203303</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>227317</t>
+          <t>228623</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,76%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36866</t>
+          <t>35828</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55479</t>
+          <t>55331</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44442</t>
+          <t>44149</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65245</t>
+          <t>65011</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86601</t>
+          <t>87009</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>115009</t>
+          <t>113061</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21428</t>
+          <t>22623</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20876</t>
+          <t>20206</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>21720</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>38066</t>
+          <t>38206</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>132302</t>
+          <t>132292</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>152121</t>
+          <t>153745</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>142019</t>
+          <t>141229</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>162959</t>
+          <t>163249</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>280341</t>
+          <t>279874</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>309003</t>
+          <t>310061</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,14%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26705</t>
+          <t>26735</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43246</t>
+          <t>43688</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30802</t>
+          <t>31122</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47511</t>
+          <t>48367</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62426</t>
+          <t>62548</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>86251</t>
+          <t>85461</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10228</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21434</t>
+          <t>22509</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17886</t>
+          <t>18102</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20904</t>
+          <t>21093</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36029</t>
+          <t>36630</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95336</t>
+          <t>95412</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>113992</t>
+          <t>113454</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>102714</t>
+          <t>102618</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>121317</t>
+          <t>121272</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>203893</t>
+          <t>203640</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>229552</t>
+          <t>229483</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,1%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36353</t>
+          <t>37064</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57246</t>
+          <t>56632</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50589</t>
+          <t>51028</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73363</t>
+          <t>72805</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94573</t>
+          <t>92491</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123573</t>
+          <t>121686</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,21%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14738</t>
+          <t>15141</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29450</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>16573</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32248</t>
+          <t>31890</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35974</t>
+          <t>35329</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56492</t>
+          <t>56051</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>130352</t>
+          <t>128680</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>153681</t>
+          <t>152525</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>109407</t>
+          <t>109953</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>133484</t>
+          <t>133336</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>247274</t>
+          <t>245639</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>278859</t>
+          <t>280871</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,42%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>133694</t>
+          <t>134541</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>169164</t>
+          <t>170311</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>168476</t>
+          <t>168533</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208834</t>
+          <t>209425</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>313820</t>
+          <t>313839</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>366123</t>
+          <t>365110</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45850</t>
+          <t>46414</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69350</t>
+          <t>69469</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46825</t>
+          <t>49941</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>73597</t>
+          <t>73146</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>101428</t>
+          <t>102268</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137235</t>
+          <t>137365</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>477575</t>
+          <t>479691</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>516583</t>
+          <t>518918</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>473417</t>
+          <t>470960</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>516590</t>
+          <t>513957</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>961303</t>
+          <t>961615</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1020206</t>
+          <t>1020835</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,44%</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17293</t>
+          <t>17394</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33436</t>
+          <t>32184</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>14551</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28586</t>
+          <t>28032</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35340</t>
+          <t>34173</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56538</t>
+          <t>56401</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17602</t>
+          <t>18101</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>8777</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22166</t>
+          <t>22527</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18738</t>
+          <t>18723</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34871</t>
+          <t>34624</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85072</t>
+          <t>85880</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>102122</t>
+          <t>102543</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>97238</t>
+          <t>97141</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>115473</t>
+          <t>115304</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>188153</t>
+          <t>187171</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>212817</t>
+          <t>213262</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,4%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24355</t>
+          <t>24132</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40390</t>
+          <t>40074</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20298</t>
+          <t>20409</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36669</t>
+          <t>36255</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49232</t>
+          <t>49681</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70500</t>
+          <t>73435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8361</t>
+          <t>8209</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19349</t>
+          <t>19136</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9493</t>
+          <t>9621</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21049</t>
+          <t>21607</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>20669</t>
+          <t>20081</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>38156</t>
+          <t>36408</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>147906</t>
+          <t>147827</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>166031</t>
+          <t>166184</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>166608</t>
+          <t>167650</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>185428</t>
+          <t>185959</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>320356</t>
+          <t>319664</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>346819</t>
+          <t>346466</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,18%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22033</t>
+          <t>22123</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37537</t>
+          <t>37024</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21831</t>
+          <t>21899</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37848</t>
+          <t>38044</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>48705</t>
+          <t>48485</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>69865</t>
+          <t>70629</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18996</t>
+          <t>19068</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10939</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23755</t>
+          <t>23010</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>21072</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37432</t>
+          <t>39073</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101982</t>
+          <t>101980</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119101</t>
+          <t>119647</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>107692</t>
+          <t>108800</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126615</t>
+          <t>126752</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>216344</t>
+          <t>214747</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>242129</t>
+          <t>241588</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,31%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16363</t>
+          <t>17217</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33824</t>
+          <t>33707</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12342</t>
+          <t>12613</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26423</t>
+          <t>26690</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33731</t>
+          <t>33091</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54046</t>
+          <t>55096</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14935</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29836</t>
+          <t>29232</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>9946</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23076</t>
+          <t>22782</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28461</t>
+          <t>28251</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47667</t>
+          <t>47697</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>146051</t>
+          <t>146348</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>166077</t>
+          <t>167099</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>156457</t>
+          <t>155701</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>173961</t>
+          <t>173677</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>308576</t>
+          <t>308881</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>335783</t>
+          <t>335966</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,26%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95230</t>
+          <t>94185</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>125865</t>
+          <t>125738</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>82312</t>
+          <t>83262</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>111990</t>
+          <t>112009</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>183535</t>
+          <t>185984</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>228850</t>
+          <t>226982</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46206</t>
+          <t>46880</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69861</t>
+          <t>70808</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49874</t>
+          <t>50527</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>76505</t>
+          <t>76109</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>103674</t>
+          <t>103689</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>139203</t>
+          <t>137127</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>503032</t>
+          <t>500158</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>537980</t>
+          <t>537504</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>547655</t>
+          <t>548146</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>584137</t>
+          <t>584236</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1061791</t>
+          <t>1062684</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1112951</t>
+          <t>1111404</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2901-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2901-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26580</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19434</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>34788</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12,81%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>22,94%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>18287</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12853</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>26049</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>12130</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>25074</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>13,31%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,36%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18,96%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>26580</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>20104</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>35432</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>17,53%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35932</t>
+          <t>35529</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54418</t>
+          <t>55797</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10750</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6529</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17118</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7,09%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11,29%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>8750</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4597</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14206</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4870</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14634</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>6,37%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>10750</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5999</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>16257</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>7,09%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13495</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26888</t>
+          <t>27842</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>114334</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>105039</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122106</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>75,39%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>69,26%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>80,51%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>110326</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101914</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117526</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>102954</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>118150</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>80,32%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>74,19%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>85,56%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>114334</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>104844</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121997</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>75,39%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>212915</t>
+          <t>212834</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>235604</t>
+          <t>235909</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,62%</t>
         </is>
       </c>
     </row>
@@ -1061,57 +1061,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>151664</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>151664</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>151664</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>137364</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>137364</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>137364</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>151664</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>151664</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>151664</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>47855</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>38670</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>58513</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>22,78%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>18,41%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>27,85%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>36131</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>28923</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>45955</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>28761</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>45635</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>18,82%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23,94%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>47855</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>38175</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>58642</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>22,78%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>72062</t>
+          <t>71931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>97157</t>
+          <t>97665</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -1296,102 +1296,102 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>8882</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>20774</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>6,76%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>9,89%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>12979</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>8462</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>19253</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>8326</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>19477</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>6,76%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>10,03%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>14202</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>9365</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>20989</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>4,34%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>10,15%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>27180</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>19684</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>36019</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>6,76%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>4,46%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>27180</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>20195</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>35953</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>148023</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>137035</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>158260</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>70,46%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>65,23%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>75,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>142829</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>132015</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>150423</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>132010</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>150858</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>74,41%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>68,78%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>78,37%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>148023</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>136477</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>157852</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>70,46%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>64,96%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>276855</t>
+          <t>276948</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>304773</t>
+          <t>304603</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,77%</t>
         </is>
       </c>
     </row>
@@ -1517,57 +1517,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>210079</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>210079</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>210079</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>307</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>191939</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>191939</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>191939</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>210079</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>210079</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>210079</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1634,72 +1634,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23139</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>17066</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>30143</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>15,74%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>11,61%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>20,5%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>26372</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19919</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>33897</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>20053</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>33072</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>19,23%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>14,53%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>24,72%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>23139</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>16394</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>30680</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>15,74%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40012</t>
+          <t>39928</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59625</t>
+          <t>60468</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -1747,72 +1747,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14697</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9633</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21356</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,55%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14,53%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9281</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5417</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14270</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5061</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>13954</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,77%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,41%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>14697</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9336</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>21251</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,0%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>17332</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32200</t>
+          <t>31505</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -1860,72 +1860,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>109168</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>99855</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>116727</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>74,26%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>67,93%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>79,4%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>101477</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>93523</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>109446</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>93789</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>108959</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>74,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>68,2%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>79,81%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>109168</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>100380</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>118022</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>74,26%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>198605</t>
+          <t>198721</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>221098</t>
+          <t>221991</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,13%</t>
         </is>
       </c>
     </row>
@@ -1978,52 +1978,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>147004</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>147004</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>147004</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>137130</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>137130</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>137130</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>147004</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>147004</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>147004</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2090,72 +2090,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>37186</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>28405</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>47989</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,17%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>23,95%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>39150</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>30696</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>50337</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>30597</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>50797</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>19,33%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>15,16%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>24,85%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>37186</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>28565</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>46316</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>18,56%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62869</t>
+          <t>64442</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90699</t>
+          <t>90217</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -2203,72 +2203,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9026</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5351</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14995</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>7,48%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>7136</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>3354</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>12438</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3539</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>13227</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>3,52%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>9026</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>5271</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>15203</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>10563</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23146</t>
+          <t>24190</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -2316,72 +2316,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>154188</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143231</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>163150</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>76,94%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>71,47%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>81,41%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>156261</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>144566</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>165865</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>144315</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>165956</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>77,15%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>71,37%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>81,89%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>154188</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143361</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>162775</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>76,94%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>295172</t>
+          <t>296271</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>325233</t>
+          <t>323611</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,31%</t>
         </is>
       </c>
     </row>
@@ -2429,57 +2429,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>200400</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>200400</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>200400</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>202547</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>202547</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>202547</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>200400</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>200400</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>200400</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2546,72 +2546,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>134759</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>119526</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>152971</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>19,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>16,85%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>21,57%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>119941</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>105748</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>135276</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>105736</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>137502</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>17,93%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>15,81%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>20,22%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>134759</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>117588</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>150193</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>19,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>16,58%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>232945</t>
+          <t>231531</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>278081</t>
+          <t>279211</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -2659,72 +2659,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>48675</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>38025</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60303</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>6,86%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>38146</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>29718</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>49112</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>29670</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>47914</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>5,7%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>4,44%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>48675</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>38277</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>60056</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>73967</t>
+          <t>72659</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>103102</t>
+          <t>101493</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -2772,72 +2772,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>525713</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>507713</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>544783</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>74,13%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>71,59%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>76,82%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>762</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>510893</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>494202</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>527609</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>493259</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>527277</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>76,37%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>73,87%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>78,87%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>791</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>525713</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>506989</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>544127</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>74,13%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1010789</t>
+          <t>1009562</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1061822</t>
+          <t>1061572</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,03%</t>
         </is>
       </c>
     </row>
@@ -2885,57 +2885,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>709147</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>709147</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>709147</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1001</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>668980</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>668980</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>668980</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>709147</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>709147</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>709147</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3066,7 +3066,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>32518</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24486</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>42787</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>21,55%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16,22%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>28,35%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>25557</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>18760</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>34295</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>18507</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>33957</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>18,34%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,46%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,61%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>32518</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>24297</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>41208</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>21,55%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46616</t>
+          <t>47366</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69740</t>
+          <t>71558</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11021</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6588</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17215</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11,41%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>5288</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2084</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10424</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2338</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>10540</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>3,79%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,48%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>11021</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6285</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17654</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10512</t>
+          <t>10520</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23306</t>
+          <t>23387</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>107384</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>96801</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>116342</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>71,15%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>64,14%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>77,09%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>108513</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>98892</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>115803</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>99730</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>116041</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>77,87%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>70,96%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>83,1%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>107384</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>98052</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>116164</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>71,15%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>203303</t>
+          <t>201704</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>228623</t>
+          <t>227477</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,36%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>150924</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>150924</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>150924</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>139357</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>150924</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>150924</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>150924</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>53793</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>44501</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>64937</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>24,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>20,21%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>29,49%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>45905</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>35828</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>55331</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>37066</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>55354</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>22,53%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>17,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>27,15%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>53793</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>44149</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>65011</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>24,43%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87009</t>
+          <t>86339</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>113061</t>
+          <t>113800</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>13531</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>8372</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>20265</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>15161</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>9966</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>22623</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>9641</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>21788</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>7,44%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>11,1%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>13531</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>8666</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>20206</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>21011</t>
+          <t>21322</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>38206</t>
+          <t>38421</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>152841</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>141959</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>162522</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>69,42%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>64,48%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>73,82%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>142720</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>132292</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>153745</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>131386</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>151741</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>70,03%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>64,92%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>75,44%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>152841</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>141229</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>163249</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>69,42%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>279874</t>
+          <t>280095</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>310061</t>
+          <t>310774</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,3%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>220165</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>220165</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>220165</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>315</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>203786</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>203786</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>203786</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>220165</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>220165</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>220165</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>38951</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>30567</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>48929</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>23,81%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>18,68%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>29,91%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>34394</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>26735</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>43688</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>26619</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>43054</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>22,23%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>17,28%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>28,24%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>38951</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>31122</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>48367</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>23,81%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62548</t>
+          <t>62797</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>85461</t>
+          <t>86810</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12375</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8076</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18483</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,56%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,3%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>15345</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10377</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>22509</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10336</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>21705</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,92%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,71%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12375</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7293</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>18102</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,56%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21093</t>
+          <t>20569</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36630</t>
+          <t>36674</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>112277</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>101337</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>122114</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>68,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>61,94%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>74,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>104962</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>95412</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>113454</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>95393</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>114189</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>67,85%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>61,68%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>73,34%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>112277</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>102618</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>121272</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>68,63%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>203640</t>
+          <t>202314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>229483</t>
+          <t>229434</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,08%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>163603</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>163603</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>163603</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>154701</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>154701</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>154701</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>163603</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>163603</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>163603</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4602,72 +4602,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>61915</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>51547</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>73700</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>29,9%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>24,89%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>35,59%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>45952</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>37064</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>56632</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>36962</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>56479</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>21,93%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17,69%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>27,03%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>61915</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>51028</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>72805</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>29,9%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92491</t>
+          <t>92994</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121686</t>
+          <t>123148</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,56%</t>
         </is>
       </c>
     </row>
@@ -4715,72 +4715,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23507</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16219</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>31732</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>11,35%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7,83%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>15,32%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>21749</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>15141</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>30206</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>15232</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>29798</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>10,38%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>14,42%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>23507</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>16573</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>31890</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>11,35%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35329</t>
+          <t>35903</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56051</t>
+          <t>57517</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -4828,72 +4828,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>121657</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>110160</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>133069</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>58,75%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>53,2%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>64,26%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>141831</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>128680</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>152525</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>129722</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>152736</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>67,69%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>61,41%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>72,79%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>121657</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>109953</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>133336</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>58,75%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>245639</t>
+          <t>246370</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>280871</t>
+          <t>279264</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,03%</t>
         </is>
       </c>
     </row>
@@ -4941,57 +4941,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>207079</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>207079</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>207079</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>209532</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>209532</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>209532</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>207079</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>207079</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>207079</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5058,72 +5058,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>187178</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>168099</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>206949</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>25,23%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>22,66%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>27,9%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>151808</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>134541</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>170311</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>134546</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>169791</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>21,46%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>19,02%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>24,08%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>187178</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>168533</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>209425</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>25,23%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>22,72%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>313839</t>
+          <t>314199</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>365110</t>
+          <t>366253</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -5171,72 +5171,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60435</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>48114</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>73102</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>8,15%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>9,86%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>57543</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>46414</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>69469</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>46183</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>70340</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>8,13%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>9,82%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>60435</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>49941</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>73146</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>8,15%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>102268</t>
+          <t>102309</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137365</t>
+          <t>136755</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -5284,72 +5284,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>494160</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>472145</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>515498</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>66,62%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>63,65%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>69,5%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>498026</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>479691</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>518918</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>479121</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>517833</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>70,4%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>67,81%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>73,36%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>494160</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>470960</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>513957</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>66,62%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>961615</t>
+          <t>962013</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1020835</t>
+          <t>1018349</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,27%</t>
         </is>
       </c>
     </row>
@@ -5397,57 +5397,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>741772</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>741772</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>741772</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1019</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>707376</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>707376</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>707376</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>741772</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>741772</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>741772</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5578,7 +5578,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5746,72 +5746,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20677</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14044</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29024</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20,4%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>24463</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17394</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>32184</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>17217</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>32038</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>18,86%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,81%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>20677</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>14551</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>28032</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>14,53%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34173</t>
+          <t>35812</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56401</t>
+          <t>57022</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -5859,72 +5859,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14723</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9572</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21723</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>15,27%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>10736</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6885</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18101</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6356</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17533</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>8,28%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>13,95%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>14723</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>8777</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22527</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>10,35%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18723</t>
+          <t>18021</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34624</t>
+          <t>34663</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -5972,72 +5972,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>106900</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>98312</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>115198</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>75,12%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>69,09%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>80,95%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>94511</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>85880</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>102543</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>85452</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>102913</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>72,86%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>66,21%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>79,06%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>106900</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>97141</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>115304</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>75,12%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>187171</t>
+          <t>188701</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>213262</t>
+          <t>213208</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,38%</t>
         </is>
       </c>
     </row>
@@ -6085,57 +6085,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>142300</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>142300</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>142300</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>129711</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>129711</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>129711</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>142300</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>142300</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>142300</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6202,72 +6202,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>27849</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>20636</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>36121</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>12,7%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9,41%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>16,48%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>31995</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>24132</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>40074</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>24379</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>40538</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>15,81%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>27849</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>20409</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>36255</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>12,7%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49681</t>
+          <t>48692</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73435</t>
+          <t>71283</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -6320,67 +6320,67 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>14718</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>9621</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>22417</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>6,71%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>10,23%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>13060</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>8209</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>19136</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>8467</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>18994</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>6,45%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>9,46%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>14718</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>9621</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>21607</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>6,71%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>20081</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36408</t>
+          <t>36569</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -6428,72 +6428,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>176650</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>166618</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>185521</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>80,58%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>76,01%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>84,63%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>157330</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>147827</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>166184</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>147899</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>166705</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>77,74%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>73,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>82,11%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>176650</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>167650</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>185959</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>80,58%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>319664</t>
+          <t>319661</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>346466</t>
+          <t>346517</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,19%</t>
         </is>
       </c>
     </row>
@@ -6541,57 +6541,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>219218</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>219218</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>219218</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>326</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>202386</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>202386</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>202386</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>219218</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>219218</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>219218</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6658,72 +6658,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>29388</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21953</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>37519</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>17,97%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>13,42%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>22,94%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>29045</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>22123</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>37024</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>22016</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>37432</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>18,98%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>14,46%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>24,2%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>29388</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>21899</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>38044</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>17,97%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>48485</t>
+          <t>48244</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>70629</t>
+          <t>70216</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -6771,72 +6771,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16341</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10513</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>24125</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,99%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14,75%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>12574</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7800</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>19068</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8126</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>19190</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,22%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,46%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>16341</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>10302</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>23010</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21072</t>
+          <t>21190</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39073</t>
+          <t>38161</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -6884,72 +6884,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>117833</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>108841</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>127335</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>72,04%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>66,54%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>77,85%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>111394</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>101980</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>119647</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>102820</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>120287</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>72,8%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>66,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>78,19%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>117833</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>108800</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>126752</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>72,04%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>214747</t>
+          <t>215454</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>241588</t>
+          <t>241435</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,26%</t>
         </is>
       </c>
     </row>
@@ -6997,57 +6997,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>163562</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>163562</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>163562</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>153013</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>153013</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>153013</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>163562</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>163562</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>163562</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>18783</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12480</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>26667</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,37%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>13,3%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>24478</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>17217</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>33707</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>17534</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>33081</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>12,06%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,48%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>16,6%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>18783</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>12613</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>26690</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,37%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33091</t>
+          <t>34029</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55096</t>
+          <t>55128</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -7227,72 +7227,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>15906</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>10614</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23417</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7,93%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>11,68%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>21513</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>14421</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>29232</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>15004</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>29715</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>10,6%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>14,4%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>15906</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>9946</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>22782</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28251</t>
+          <t>28314</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47697</t>
+          <t>48268</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -7340,72 +7340,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>165799</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>155117</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>173823</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>82,7%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>77,37%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>86,7%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>157027</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>146348</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>167099</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>146184</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>166218</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>77,35%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>72,09%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>82,31%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>165799</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>155701</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>173677</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>82,7%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>308881</t>
+          <t>309393</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>335966</t>
+          <t>335633</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,18%</t>
         </is>
       </c>
     </row>
@@ -7453,57 +7453,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>200488</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>200488</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>200488</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>203017</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>203017</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>203017</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>200488</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>200488</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>200488</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>96697</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>82070</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>113850</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>13,33%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>11,31%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>15,69%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>109982</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>94185</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>125738</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>94561</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>125295</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>15,98%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>18,27%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>96697</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>83262</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>112009</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>13,33%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>185984</t>
+          <t>185165</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>226982</t>
+          <t>229681</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -7688,67 +7688,67 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>61689</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>49539</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74131</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>10,22%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
           <t>57883</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>46880</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>70808</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>46867</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>70660</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>8,41%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>6,81%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>10,29%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>61689</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>50527</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>76109</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>8,5%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>103689</t>
+          <t>104580</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137127</t>
+          <t>138082</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -7796,72 +7796,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>567182</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>548657</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>584675</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>78,17%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>75,62%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>80,58%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>786</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>520263</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>500158</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>537504</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>501991</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>539107</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>75,61%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>72,68%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>78,11%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>809</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>567182</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>548146</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>584236</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>78,17%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1062684</t>
+          <t>1059297</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1111404</t>
+          <t>1109957</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,51%</t>
         </is>
       </c>
     </row>
@@ -7909,57 +7909,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1037</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>725568</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>725568</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>725568</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1036</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>688128</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>688128</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>688128</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1037</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>725568</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>725568</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>725568</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
